--- a/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:56:22+00:00</t>
+    <t>2026-07-31T09:38:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$87</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2641" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3219" uniqueCount="555">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:38:41+00:00</t>
+    <t>2026-07-31T12:59:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1535,6 +1535,10 @@
     <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension('http://hl7.fr/ig/.../StructureDefinition/fr-imaging-note-type-extension')}
+</t>
+  </si>
+  <si>
     <t>Request.note</t>
   </si>
   <si>
@@ -1544,32 +1548,71 @@
     <t>ClinicalStatement.additionalText</t>
   </si>
   <si>
+    <t>ServiceRequest.note:finaliteExamen</t>
+  </si>
+  <si>
+    <t>finaliteExamen</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:finaliteExamen.id</t>
+  </si>
+  <si>
     <t>ServiceRequest.note.id</t>
   </si>
   <si>
+    <t>ServiceRequest.note:finaliteExamen.extension</t>
+  </si>
+  <si>
     <t>ServiceRequest.note.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>ServiceRequest.note.extension:imagingRequest</t>
-  </si>
-  <si>
-    <t>imagingRequest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-imaging-request-extension|0.1.0}
+    <t>ServiceRequest.note:finaliteExamen.extension:noteType</t>
+  </si>
+  <si>
+    <t>noteType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-note-type-extension|0.1.0}
 </t>
   </si>
   <si>
-    <t>FR Imaging Request Extension</t>
-  </si>
-  <si>
-    <t>Extension permettant de renseigner les notes associées à une demande d’examen d’imagerie, notamment la finalité de l’examen et la justification de la demande.</t>
+    <t>FR Note Type Extension</t>
+  </si>
+  <si>
+    <t>Extension permettant de préciser le type d'information contenu dans une note associée à une demande d'examen d'imagerie.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:finaliteExamen.extension:noteType.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note.extension.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:finaliteExamen.extension:noteType.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note.extension.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:finaliteExamen.extension:noteType.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-note-type-extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:finaliteExamen.extension:noteType.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note.extension.value[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-note-type|0.1.0</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:finaliteExamen.author[x]</t>
   </si>
   <si>
     <t>ServiceRequest.note.author[x]</t>
@@ -1594,6 +1637,9 @@
     <t>Act.participant[typeCode=AUT].role</t>
   </si>
   <si>
+    <t>ServiceRequest.note:finaliteExamen.time</t>
+  </si>
+  <si>
     <t>ServiceRequest.note.time</t>
   </si>
   <si>
@@ -1607,6 +1653,9 @@
   </si>
   <si>
     <t>Act.effectiveTime</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:finaliteExamen.text</t>
   </si>
   <si>
     <t>ServiceRequest.note.text</t>
@@ -1626,6 +1675,42 @@
   </si>
   <si>
     <t>Act.text</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande</t>
+  </si>
+  <si>
+    <t>justificationDemande</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.extension:noteType</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.extension:noteType.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.extension:noteType.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.extension:noteType.url</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.extension:noteType.value[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.author[x]</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.time</t>
+  </si>
+  <si>
+    <t>ServiceRequest.note:justificationDemande.text</t>
   </si>
   <si>
     <t>ServiceRequest.patientInstruction</t>
@@ -1978,12 +2063,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO71"/>
+  <dimension ref="A1:AO87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.5" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.80078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.7265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.8984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2008,7 +2093,7 @@
     <col min="25" max="25" width="160.17578125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="70.0234375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -9241,7 +9326,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>482</v>
       </c>
@@ -9254,7 +9339,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>80</v>
@@ -9314,16 +9399,14 @@
         <v>81</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>482</v>
@@ -9341,41 +9424,43 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>336</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>81</v>
@@ -9384,13 +9469,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>155</v>
+        <v>483</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>156</v>
+        <v>484</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>157</v>
+        <v>485</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9441,53 +9526,53 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>158</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>81</v>
+        <v>487</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>81</v>
+        <v>336</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>159</v>
+        <v>488</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>208</v>
+        <v>81</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9499,17 +9584,15 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>491</v>
+        <v>156</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9546,31 +9629,31 @@
         <v>81</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>81</v>
@@ -9590,23 +9673,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -9618,13 +9699,13 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>495</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>496</v>
+        <v>136</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>497</v>
+        <v>137</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9663,16 +9744,16 @@
         <v>81</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>164</v>
@@ -9705,45 +9786,45 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>502</v>
-      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -9792,28 +9873,28 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>164</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -9824,10 +9905,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9847,16 +9928,16 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>382</v>
+        <v>155</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>506</v>
+        <v>156</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>507</v>
+        <v>157</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9907,7 +9988,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>508</v>
+        <v>158</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9919,16 +10000,16 @@
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>509</v>
+        <v>159</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -9939,10 +10020,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9950,10 +10031,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -9962,16 +10043,16 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>511</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>512</v>
+        <v>136</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>513</v>
+        <v>137</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10010,40 +10091,40 @@
         <v>81</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>514</v>
+        <v>164</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>515</v>
+        <v>81</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
@@ -10054,10 +10135,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10065,7 +10146,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>90</v>
@@ -10077,25 +10158,27 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>517</v>
+        <v>173</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>81</v>
@@ -10137,10 +10220,10 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>516</v>
+        <v>176</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>90</v>
@@ -10149,16 +10232,16 @@
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>519</v>
+        <v>133</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10169,10 +10252,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10183,7 +10266,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
@@ -10195,17 +10278,15 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>521</v>
+        <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>522</v>
+        <v>179</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10215,7 +10296,7 @@
         <v>81</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>81</v>
+        <v>491</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>81</v>
@@ -10230,13 +10311,11 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>81</v>
+        <v>510</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10254,13 +10333,13 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>520</v>
+        <v>184</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
@@ -10269,23 +10348,1873 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="B74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL74" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AM74" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="D75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y82" s="2"/>
+      <c r="Z82" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AN71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO71" t="s" s="2">
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO71">
+  <autoFilter ref="A1:AO87">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10295,7 +12224,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI86">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:59:03+00:00</t>
+    <t>2026-07-31T13:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1535,7 +1535,7 @@
     <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension('http://hl7.fr/ig/.../StructureDefinition/fr-imaging-note-type-extension')}
+    <t xml:space="preserve">value:extension('http://hl7.fr/ig/.../StructureDefinition/fr-note-type-extension')}
 </t>
   </si>
   <si>
@@ -2093,7 +2093,7 @@
     <col min="25" max="25" width="160.17578125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="70.0234375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="63.09765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>

--- a/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:02:34+00:00</t>
+    <t>2026-07-31T13:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1535,7 +1535,7 @@
     <t>Any other notes and comments made about the service request. For example, internal billing notes.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension('http://hl7.fr/ig/.../StructureDefinition/fr-note-type-extension')}
+    <t xml:space="preserve">value:extension('http://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-note-type-extension')}
 </t>
   </si>
   <si>
@@ -2093,7 +2093,7 @@
     <col min="25" max="25" width="160.17578125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="63.09765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="90.09765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>

--- a/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:07:52+00:00</t>
+    <t>2026-08-03T06:54:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
